--- a/Risk_Register/GRC_Intelligence_Risk_Register_2026-09-28b.xlsx
+++ b/Risk_Register/GRC_Intelligence_Risk_Register_2026-09-28b.xlsx
@@ -1014,7 +1014,7 @@
     <row r="2" ht="18" customHeight="1" s="42">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>ARCHIVED SNAPSHOT: v13 — 2026-09-28 — NOT LIVE.  This is a frozen historical copy (same-day supplemental version; see the GRC_Intelligence_Risk_Register_2026-09-28.xlsx snapshot for v12, the initial same-day version). The current, authoritative file is GRC_Intelligence_Risk_Register.xlsx.   |   Sources: CISA KEV | US-CERT | NIST NVD | AWS/Azure Bulletins | AI Governance Updates | CISA/NSA/FBI Advisories | Intelligence_Log   |   Frameworks: NIST CSF 2.0 | ISO 27001 | NIST 800-53 | CIS Controls | NIST AI RMF | ISO 42001 | EU AI Act   |   Snapshot Date: 2026-09-28   |   See '📋 Version Log' tab for history.</t>
+          <t>ARCHIVED SNAPSHOT: v13 — 2026-09-28 — NOT LIVE.  This is a frozen historical copy (same-day supplemental version; see the GRC_Intelligence_Risk_Register_2026-09-28.xlsx snapshot for v12, the initial same-day version). The current, authoritative file is GRC_Intelligence_Risk_Register.xlsx.   |   Sources: CISA KEV | US-CERT | NIST NVD | AWS/Azure Bulletins | AI Governance Updates | CISA/NSA/FBI Advisories | Supplementary news log   |   Frameworks: NIST CSF 2.0 | ISO 27001 | NIST 800-53 | CIS Controls | NIST AI RMF | ISO 42001 | EU AI Act   |   Snapshot Date: 2026-09-28   |   See '📋 Version Log' tab for history.</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="X93" s="53" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from the Intelligence_Log folder (newly granted access this run; see Version Log v13 note). Critical per Vercel/Next.js's own GHSA-vcvr-r3jv-pc5j advisory; no confirmed active exploitation identified in sources reviewed, hence Likelihood scored below this week's confirmed-actively-exploited findings despite the vendor's own "Critical" label. Conditional precondition (untrusted input into ImageResponse) narrows real-world reach, similar to this week's WordPress Core RFI entry (RR-087).</t>
+          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from a supplementary news log (see Version Log v13 note). Critical per Vercel/Next.js's own GHSA-vcvr-r3jv-pc5j advisory; no confirmed active exploitation identified in sources reviewed, hence Likelihood scored below this week's confirmed-actively-exploited findings despite the vendor's own "Critical" label. Conditional precondition (untrusted input into ImageResponse) narrows real-world reach, similar to this week's WordPress Core RFI entry (RR-087).</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="X94" s="53" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from the Intelligence_Log folder (newly granted access this run; see Version Log v13 note). CVSS 8.1. Unauthenticated, pre-auth SQLi with direct database access (mailbox credentials, stored messages). Canadian Centre for Cyber Security advisory (AV26-503, 2026-09-21) cited open-source reporting of active exploitation; not confirmed added to CISA's KEV catalog as of this entry — source labeled accordingly rather than as "CISA KEV." Roundcube has a documented history of repeated targeting, including a China-nexus actor (UNK_MassTraction, reported by Proofpoint) exploiting prior Roundcube CVEs for web-shell/VShell deployment. Given the CVSS/exploitation profile, this is a reasonable candidate for a full case-study bundle if the operator wants deeper coverage — flagged for that judgment call rather than decided unilaterally in this supplemental pass.</t>
+          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from a supplementary news log (see Version Log v13 note). CVSS 8.1. Unauthenticated, pre-auth SQLi with direct database access (mailbox credentials, stored messages). Canadian Centre for Cyber Security advisory (AV26-503, 2026-09-21) cited open-source reporting of active exploitation; not confirmed added to CISA's KEV catalog as of this entry — source labeled accordingly rather than as "CISA KEV." Roundcube has a documented history of repeated targeting, including a China-nexus actor (UNK_MassTraction, reported by Proofpoint) exploiting prior Roundcube CVEs for web-shell/VShell deployment. Given the CVSS/exploitation profile, this is a reasonable candidate for a full case-study bundle if the operator wants deeper coverage — flagged for that judgment call rather than decided unilaterally in this supplemental pass.</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="X95" s="53" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from the Intelligence_Log folder (newly granted access this run; see Version Log v13 note). PROGRAM GAP IDENTIFIED: this CVE was added to CISA KEV on 2026-08-05 (within the 2026-08-03–2026-08-10 report window, v9) but does not appear in this program's v9 register additions (RR-045–RR-050) — it was missed at the time, not deliberately screened out; logged now rather than left permanently unswept, consistent with this program's no-silent-drop principle, dated to this week's genuinely new information (the 2026-09-24 CISA update flagging ransomware-campaign use) rather than backdated to August. CVSS 9.8 (multiple trackers). Recommend the operator treat this as a signal to spot-check other August/September weeks for similar gaps, not just this one CVE.</t>
+          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from a supplementary news log (see Version Log v13 note). PROGRAM GAP IDENTIFIED: this CVE was added to CISA KEV on 2026-08-05 (within the 2026-08-03–2026-08-10 report window, v9) but does not appear in this program's v9 register additions (RR-045–RR-050) — it was missed at the time, not deliberately screened out; logged now rather than left permanently unswept, consistent with this program's no-silent-drop principle, dated to this week's genuinely new information (the 2026-09-24 CISA update flagging ransomware-campaign use) rather than backdated to August. CVSS 9.8 (multiple trackers). Recommend the operator treat this as a signal to spot-check other August/September weeks for similar gaps, not just this one CVE.</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="X96" s="53" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from the Intelligence_Log folder (newly granted access this run; see Version Log v13 note). Non-CVE governance/threat-intelligence item, logged per this program's precedent for non-technical disclosure items (cf. RR-077, RR-078). Managed file-transfer platforms are a recurring ransomware-gang target class (Clop's history with Accellion FTA, GoAnywhere MFT, SolarWinds Serv-U, Cleo, and MOVEit Transfer is the direct precedent cited in reporting) — flagged for governance awareness and vendor-risk-register visibility rather than as an active technical finding.</t>
+          <t>SUPPLEMENTAL ENTRY — added after the initial 2026-09-28 sweep, sourced from a supplementary news log (see Version Log v13 note). Non-CVE governance/threat-intelligence item, logged per this program's precedent for non-technical disclosure items (cf. RR-077, RR-078). Managed file-transfer platforms are a recurring ransomware-gang target class (Clop's history with Accellion FTA, GoAnywhere MFT, SolarWinds Serv-U, Cleo, and MOVEit Transfer is the direct precedent cited in reporting) — flagged for governance awareness and vendor-risk-register visibility rather than as an active technical finding.</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G17" s="41" t="inlineStr">
         <is>
-          <t>SAME-DAY SUPPLEMENTAL UPDATE to v12, issued after v12 was already delivered to the operator. Prompted by the operator flagging that this session had not been reading C:\Projects\Intelligence_Log\ — a daily-updated log the operator expects this program to cross-reference for case triage going forward. Access to that folder was requested and granted mid-run (it sits outside the two roots this task was originally scoped to: GRC_Portfolio and GRC_Internal). Reviewed all Intelligence_Log entries falling in this run's report period (2026-09-21 through 2026-09-25; no entries exist yet for 9/26-9/28) plus the folder's own 2026-09-28 weekly synthesis. NOTE ON THE FOLDER'S NATURE: Intelligence_Log is run by a separate automation (a "Career Strategist" agent, per its own weekly synthesis header) whose primary purpose is the operator's personal career-strategy and certification-study tracking, not a curated GRC case-triage feed — its cybersecurity bullets are incidental mentions inside career-focused daily notes, not pre-vetted candidates. Four items from those daily notes were independently verified against primary/vendor sources and met this program's logging threshold; none were already captured by the initial 2026-09-28 sweep. Added: Next.js next/og ImageResponse RCE (CVE-2026-94545, Critical per Vercel, disclosed 2026-09-22, conditional on untrusted input reaching ImageResponse); Roundcube Webmail pre-auth SQL injection (CVE-2026-48842, CVSS 8.1, patched May 2026 but newly confirmed under active exploitation via a Canadian Centre for Cyber Security advisory dated 2026-09-21 — a strong candidate for a full case-study bundle given its unauthenticated profile and documented history of nation-state targeting, flagged for the operator's own bundle-upgrade decision rather than decided unilaterally here); JetBrains TeamCity auth-bypass-to-RCE (CVE-2026-63077, CVSS 9.8) — a genuine PROGRAM GAP: this CVE was KEV-listed 2026-08-05, inside the v9 report window (2026-08-03 to 2026-08-10), but does not appear among RR-045–RR-050 (v9's additions); it was missed at the time, not deliberately screened out, and is logged now (dated to this week's new information — CISA's 2026-09-24 update flagging confirmed ransomware-campaign use — rather than backdated to August) per this program's no-silent-drop principle; and Kiteworks' precautionary customer-wide server-shutdown advisory (non-CVE, 2026-09-25, based on law-enforcement threat intelligence, no confirmed vulnerability or breach) as a governance/vendor-risk item given the managed-file-transfer product class's history as a ransomware target (Clop / Accellion FTA / GoAnywhere MFT / MOVEit Transfer precedent, cited directly in the source reporting). All four logged register-only pending the operator's review; none were built into full case-study bundles or added to this week's executive report narrative in this pass, to keep the supplemental update itself reviewable as a discrete unit — recommend the operator decide whether Roundcube and/or TeamCity warrant upgrading to full bundles, and whether the TeamCity gap warrants a spot-check of other August/September windows for similar misses. PROCESS NOTE: this is the first time this program has issued a same-day supplemental version; the dated-snapshot filename convention (YYYY-MM-DD) does not natively support two snapshots on one calendar date, so this snapshot uses a "b" suffix (GRC_Intelligence_Risk_Register_2026-09-28b.xlsx) — flagged here as a naming-convention gap in Section 7 of the monitoring prompt worth a formal fix if same-day supplements become a recurring pattern, e.g. adding a run-sequence suffix to the convention. Dedup check performed against all CVE/Advisory IDs on file for these 4 additions; no duplicate rows found. Column-alignment spot check run and passed (G/H populated, K/L numeric 1-5, M=K×L formula verified, INHERENT RISK and NOTES populated for all 4 rows). Going forward, C:\Projects\Intelligence_Log\ should be read as a supplementary cross-check source in Step 3 of every future run, per the operator's explicit instruction — recorded in this program's own task configuration, not only in this log entry, so it survives into future runs regardless of who or what executes them.</t>
+          <t>SAME-DAY SUPPLEMENTAL UPDATE to v12, issued after v12 was already delivered to the operator. Prompted by a review of a supplementary daily news log that this program had not previously cross-referenced. Reviewed all log entries falling in this run's report period (2026-09-21 through 2026-09-25; no entries exist yet for 9/26-9/28). The log is a general news feed rather than a curated GRC case-triage source, so its cybersecurity items are incidental mentions, not pre-vetted candidates. Four items from that log were independently verified against primary/vendor sources and met this program's logging threshold; none were already captured by the initial 2026-09-28 sweep. Added: Next.js next/og ImageResponse RCE (CVE-2026-94545, Critical per Vercel, disclosed 2026-09-22, conditional on untrusted input reaching ImageResponse); Roundcube Webmail pre-auth SQL injection (CVE-2026-48842, CVSS 8.1, patched May 2026 but newly confirmed under active exploitation via a Canadian Centre for Cyber Security advisory dated 2026-09-21 — a strong candidate for a full case-study bundle given its unauthenticated profile and documented history of nation-state targeting, flagged for the operator's own bundle-upgrade decision rather than decided unilaterally here); JetBrains TeamCity auth-bypass-to-RCE (CVE-2026-63077, CVSS 9.8) — a genuine PROGRAM GAP: this CVE was KEV-listed 2026-08-05, inside the v9 report window (2026-08-03 to 2026-08-10), but does not appear among RR-045–RR-050 (v9's additions); it was missed at the time, not deliberately screened out, and is logged now (dated to this week's new information — CISA's 2026-09-24 update flagging confirmed ransomware-campaign use — rather than backdated to August) per this program's no-silent-drop principle; and Kiteworks' precautionary customer-wide server-shutdown advisory (non-CVE, 2026-09-25, based on law-enforcement threat intelligence, no confirmed vulnerability or breach) as a governance/vendor-risk item given the managed-file-transfer product class's history as a ransomware target (Clop / Accellion FTA / GoAnywhere MFT / MOVEit Transfer precedent, cited directly in the source reporting). All four logged register-only pending the operator's review; none were built into full case-study bundles or added to this week's executive report narrative in this pass, to keep the supplemental update itself reviewable as a discrete unit — recommend the operator decide whether Roundcube and/or TeamCity warrant upgrading to full bundles, and whether the TeamCity gap warrants a spot-check of other August/September windows for similar misses. PROCESS NOTE: this is the first time this program has issued a same-day supplemental version; the dated-snapshot filename convention (YYYY-MM-DD) does not natively support two snapshots on one calendar date, so this snapshot uses a "b" suffix (GRC_Intelligence_Risk_Register_2026-09-28b.xlsx) — flagged here as a naming-convention gap in Section 7 of the monitoring prompt worth a formal fix if same-day supplements become a recurring pattern, e.g. adding a run-sequence suffix to the convention. Dedup check performed against all CVE/Advisory IDs on file for these 4 additions; no duplicate rows found. Column-alignment spot check run and passed (G/H populated, K/L numeric 1-5, M=K×L formula verified, INHERENT RISK and NOTES populated for all 4 rows). Going forward, the supplementary news log should be read as a cross-check source in Step 3 of every future run, as recorded in this program's task configuration.</t>
         </is>
       </c>
     </row>
